--- a/database/HEE_and_Brazil.xlsx
+++ b/database/HEE_and_Brazil.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18866,7 +18866,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="L136" t="inlineStr"/>
@@ -18909,7 +18909,7 @@
       </c>
       <c r="AD136" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="AE136" t="n">
@@ -25289,7 +25289,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -25354,7 +25354,7 @@
       </c>
       <c r="AG186" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="AH186" t="inlineStr"/>
@@ -25734,7 +25734,7 @@
       </c>
       <c r="AD189" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="AE189" t="n">
@@ -27917,13 +27917,13 @@
       <c r="U206" t="inlineStr"/>
       <c r="V206" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="W206" t="inlineStr"/>
       <c r="X206" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="Y206" t="n">
@@ -28653,7 +28653,7 @@
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="M212" t="n">
@@ -31966,7 +31966,7 @@
       <c r="W237" t="inlineStr"/>
       <c r="X237" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="Y237" t="n">
@@ -33360,7 +33360,7 @@
       <c r="S247" t="inlineStr"/>
       <c r="T247" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="U247" t="inlineStr"/>
